--- a/clientes_banco_tbj.xlsx
+++ b/clientes_banco_tbj.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,13 +462,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>salario</t>
+          <t>poupança</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>400</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>321</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>salario</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>400</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/clientes_banco_tbj.xlsx
+++ b/clientes_banco_tbj.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,11 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>jaoo</t>
-        </is>
+      <c r="B2" t="n">
+        <v>123</v>
       </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -476,13 +474,11 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B3" t="n">
+        <v>321</v>
       </c>
       <c r="C3" t="n">
-        <v>321</v>
+        <v>123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -493,6 +489,30 @@
         <v>400</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>321</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>salario</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/clientes_banco_tbj.xlsx
+++ b/clientes_banco_tbj.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,15 +452,17 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>jaoo</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>123</v>
       </c>
-      <c r="C2" t="n">
-        <v>321</v>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>poupança</t>
+          <t>corrente</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -474,11 +476,15 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="n">
-        <v>321</v>
-      </c>
-      <c r="C3" t="n">
-        <v>123</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>joao</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,30 +495,6 @@
         <v>400</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>321</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>salario</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
